--- a/artfynd/A 2428-2025 artfynd.xlsx
+++ b/artfynd/A 2428-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135786427</v>
       </c>
       <c r="B2" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135786405</v>
       </c>
       <c r="B3" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135786429</v>
       </c>
       <c r="B4" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135786434</v>
       </c>
       <c r="B5" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135786435</v>
       </c>
       <c r="B6" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135786428</v>
       </c>
       <c r="B7" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135786430</v>
       </c>
       <c r="B8" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135786432</v>
       </c>
       <c r="B9" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 2428-2025 artfynd.xlsx
+++ b/artfynd/A 2428-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135786427</v>
       </c>
       <c r="B2" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135786405</v>
       </c>
       <c r="B3" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135786429</v>
       </c>
       <c r="B4" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135786434</v>
       </c>
       <c r="B5" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135786435</v>
       </c>
       <c r="B6" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135786428</v>
       </c>
       <c r="B7" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135786430</v>
       </c>
       <c r="B8" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135786432</v>
       </c>
       <c r="B9" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135786403</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135786406</v>
       </c>
       <c r="B11" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135786407</v>
       </c>
       <c r="B12" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135786411</v>
       </c>
       <c r="B13" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135786413</v>
       </c>
       <c r="B14" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135786414</v>
       </c>
       <c r="B15" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135786415</v>
       </c>
       <c r="B16" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>135786416</v>
       </c>
       <c r="B17" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>135786417</v>
       </c>
       <c r="B18" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>135786424</v>
       </c>
       <c r="B19" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135786433</v>
       </c>
       <c r="B20" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>135780544</v>
       </c>
       <c r="B21" t="n">
-        <v>79465</v>
+        <v>79467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>135786409</v>
       </c>
       <c r="B22" t="n">
-        <v>79465</v>
+        <v>79467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>135786431</v>
       </c>
       <c r="B23" t="n">
-        <v>79465</v>
+        <v>79467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>135786412</v>
       </c>
       <c r="B24" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>135786426</v>
       </c>
       <c r="B25" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>135780545</v>
       </c>
       <c r="B26" t="n">
-        <v>80560</v>
+        <v>80562</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>135786420</v>
       </c>
       <c r="B27" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>135786423</v>
       </c>
       <c r="B28" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>135786425</v>
       </c>
       <c r="B29" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>135786408</v>
       </c>
       <c r="B30" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>135786410</v>
       </c>
       <c r="B31" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>135786418</v>
       </c>
       <c r="B32" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>135786422</v>
       </c>
       <c r="B33" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>135786419</v>
       </c>
       <c r="B34" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>135786404</v>
       </c>
       <c r="B35" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 2428-2025 artfynd.xlsx
+++ b/artfynd/A 2428-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135786427</v>
       </c>
       <c r="B2" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135786405</v>
       </c>
       <c r="B3" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135786429</v>
       </c>
       <c r="B4" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135786434</v>
       </c>
       <c r="B5" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135786435</v>
       </c>
       <c r="B6" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135786428</v>
       </c>
       <c r="B7" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135786430</v>
       </c>
       <c r="B8" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135786432</v>
       </c>
       <c r="B9" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135786403</v>
       </c>
       <c r="B10" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135786406</v>
       </c>
       <c r="B11" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135786407</v>
       </c>
       <c r="B12" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135786411</v>
       </c>
       <c r="B13" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135786413</v>
       </c>
       <c r="B14" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135786414</v>
       </c>
       <c r="B15" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135786415</v>
       </c>
       <c r="B16" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>135786416</v>
       </c>
       <c r="B17" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>135786417</v>
       </c>
       <c r="B18" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>135786424</v>
       </c>
       <c r="B19" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135786433</v>
       </c>
       <c r="B20" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>135780544</v>
       </c>
       <c r="B21" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>135786409</v>
       </c>
       <c r="B22" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>135786431</v>
       </c>
       <c r="B23" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>135786412</v>
       </c>
       <c r="B24" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>135786426</v>
       </c>
       <c r="B25" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>135780545</v>
       </c>
       <c r="B26" t="n">
-        <v>80562</v>
+        <v>80563</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>135786404</v>
       </c>
       <c r="B35" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 2428-2025 artfynd.xlsx
+++ b/artfynd/A 2428-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135786427</v>
       </c>
       <c r="B2" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135786405</v>
       </c>
       <c r="B3" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135786429</v>
       </c>
       <c r="B4" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135786434</v>
       </c>
       <c r="B5" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135786435</v>
       </c>
       <c r="B6" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135786428</v>
       </c>
       <c r="B7" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135786430</v>
       </c>
       <c r="B8" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135786432</v>
       </c>
       <c r="B9" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 2428-2025 artfynd.xlsx
+++ b/artfynd/A 2428-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135786427</v>
       </c>
       <c r="B2" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135786405</v>
       </c>
       <c r="B3" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135786429</v>
       </c>
       <c r="B4" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135786434</v>
       </c>
       <c r="B5" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135786435</v>
       </c>
       <c r="B6" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135786428</v>
       </c>
       <c r="B7" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135786430</v>
       </c>
       <c r="B8" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135786432</v>
       </c>
       <c r="B9" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135786403</v>
       </c>
       <c r="B10" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135786406</v>
       </c>
       <c r="B11" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135786407</v>
       </c>
       <c r="B12" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135786411</v>
       </c>
       <c r="B13" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135786413</v>
       </c>
       <c r="B14" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135786414</v>
       </c>
       <c r="B15" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135786415</v>
       </c>
       <c r="B16" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>135786416</v>
       </c>
       <c r="B17" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>135786417</v>
       </c>
       <c r="B18" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>135786424</v>
       </c>
       <c r="B19" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135786433</v>
       </c>
       <c r="B20" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>135780544</v>
       </c>
       <c r="B21" t="n">
-        <v>79468</v>
+        <v>79469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>135786409</v>
       </c>
       <c r="B22" t="n">
-        <v>79468</v>
+        <v>79469</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>135786431</v>
       </c>
       <c r="B23" t="n">
-        <v>79468</v>
+        <v>79469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>135786412</v>
       </c>
       <c r="B24" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>135786426</v>
       </c>
       <c r="B25" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>135780545</v>
       </c>
       <c r="B26" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>135786420</v>
       </c>
       <c r="B27" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>135786423</v>
       </c>
       <c r="B28" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>135786425</v>
       </c>
       <c r="B29" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>135786408</v>
       </c>
       <c r="B30" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>135786410</v>
       </c>
       <c r="B31" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>135786418</v>
       </c>
       <c r="B32" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>135786422</v>
       </c>
       <c r="B33" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>135786419</v>
       </c>
       <c r="B34" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>135786404</v>
       </c>
       <c r="B35" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 2428-2025 artfynd.xlsx
+++ b/artfynd/A 2428-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135786427</v>
       </c>
       <c r="B2" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135786405</v>
       </c>
       <c r="B3" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135786429</v>
       </c>
       <c r="B4" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135786434</v>
       </c>
       <c r="B5" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135786435</v>
       </c>
       <c r="B6" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135786428</v>
       </c>
       <c r="B7" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135786430</v>
       </c>
       <c r="B8" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135786432</v>
       </c>
       <c r="B9" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135786403</v>
       </c>
       <c r="B10" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135786406</v>
       </c>
       <c r="B11" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135786407</v>
       </c>
       <c r="B12" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135786411</v>
       </c>
       <c r="B13" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135786413</v>
       </c>
       <c r="B14" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135786414</v>
       </c>
       <c r="B15" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135786415</v>
       </c>
       <c r="B16" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>135786416</v>
       </c>
       <c r="B17" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>135786417</v>
       </c>
       <c r="B18" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>135786424</v>
       </c>
       <c r="B19" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135786433</v>
       </c>
       <c r="B20" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>135780544</v>
       </c>
       <c r="B21" t="n">
-        <v>79469</v>
+        <v>79473</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>135786409</v>
       </c>
       <c r="B22" t="n">
-        <v>79469</v>
+        <v>79473</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>135786431</v>
       </c>
       <c r="B23" t="n">
-        <v>79469</v>
+        <v>79473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>135786412</v>
       </c>
       <c r="B24" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>135786426</v>
       </c>
       <c r="B25" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>135780545</v>
       </c>
       <c r="B26" t="n">
-        <v>80564</v>
+        <v>80568</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>135786420</v>
       </c>
       <c r="B27" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>135786423</v>
       </c>
       <c r="B28" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>135786425</v>
       </c>
       <c r="B29" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>135786408</v>
       </c>
       <c r="B30" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>135786410</v>
       </c>
       <c r="B31" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>135786418</v>
       </c>
       <c r="B32" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>135786422</v>
       </c>
       <c r="B33" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>135786419</v>
       </c>
       <c r="B34" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>135786404</v>
       </c>
       <c r="B35" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 2428-2025 artfynd.xlsx
+++ b/artfynd/A 2428-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135786427</v>
       </c>
       <c r="B2" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135786405</v>
       </c>
       <c r="B3" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135786429</v>
       </c>
       <c r="B4" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135786434</v>
       </c>
       <c r="B5" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135786435</v>
       </c>
       <c r="B6" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135786428</v>
       </c>
       <c r="B7" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135786430</v>
       </c>
       <c r="B8" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135786432</v>
       </c>
       <c r="B9" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135786403</v>
       </c>
       <c r="B10" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135786406</v>
       </c>
       <c r="B11" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135786407</v>
       </c>
       <c r="B12" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135786411</v>
       </c>
       <c r="B13" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135786413</v>
       </c>
       <c r="B14" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135786414</v>
       </c>
       <c r="B15" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135786415</v>
       </c>
       <c r="B16" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>135786416</v>
       </c>
       <c r="B17" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>135786417</v>
       </c>
       <c r="B18" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>135786424</v>
       </c>
       <c r="B19" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135786433</v>
       </c>
       <c r="B20" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>135780544</v>
       </c>
       <c r="B21" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>135786409</v>
       </c>
       <c r="B22" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>135786431</v>
       </c>
       <c r="B23" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>135786412</v>
       </c>
       <c r="B24" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>135786426</v>
       </c>
       <c r="B25" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>135780545</v>
       </c>
       <c r="B26" t="n">
-        <v>80568</v>
+        <v>80569</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>135786420</v>
       </c>
       <c r="B27" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>135786423</v>
       </c>
       <c r="B28" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>135786425</v>
       </c>
       <c r="B29" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>135786408</v>
       </c>
       <c r="B30" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>135786410</v>
       </c>
       <c r="B31" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>135786418</v>
       </c>
       <c r="B32" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>135786422</v>
       </c>
       <c r="B33" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>135786419</v>
       </c>
       <c r="B34" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>135786404</v>
       </c>
       <c r="B35" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
